--- a/REKAPITULASI_PRE_POST_TEST_CANVA.xlsx
+++ b/REKAPITULASI_PRE_POST_TEST_CANVA.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kuesioner" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revisi" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rekap" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kuesioner Lengkap" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensus Peserta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kuesioner" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revisi" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rekap" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kuesioner Lengkap" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,8 +44,20 @@
       <i val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +89,16 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0012284B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -103,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -129,6 +152,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -208,6 +251,130 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Sesi versus orang — kedua tes</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Sensus Peserta'!C42</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Sensus Peserta'!$B$43:$B$47</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sensus Peserta'!$C$43:$C$47</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Sensus Peserta'!D42</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Sensus Peserta'!$B$43:$B$47</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sensus Peserta'!$D$43:$D$47</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Jumlah</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
@@ -330,9 +497,8 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -453,6 +619,33 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -790,6 +983,782 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:H47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>SENSUS PESERTA — JUMLAH SESI VERSUS JUMLAH ORANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Wayground mencatat SESI, bukan orang. Satu orang yang koneksinya terputus lalu masuk kembali tercatat sebagai dua baris terpisah. Lembar ini merekonsiliasi kedua cacah tersebut sehingga setiap angka pada laporan dapat ditelusuri asalnya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>A. REKONSILIASI CACAH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Ukuran</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Pre-test</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Post-test</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Sesi terekam di ekspor</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>Baris apa adanya pada sheet Participant Data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Sesi uji perangkat lunak (QA)</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Sesi atas nama Vincent pada post-test; 15 dari 20 butir dijawab dalam 1 detik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Sesi peserta</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>Setelah sesi QA dikeluarkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Sesi ganda dari orang yang sama</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>Pre-test: Sri Suyani 3 sesi, Aqifah 2, farida johannes 2. Post-test: Yovita 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>ORANG UNIK</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>INI JAWABAN atas pertanyaan 'berapa orang'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Orang menjawab sedikitnya 1 butir</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>Pre-test: 3 orang tidak menjawab apa pun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Orang menyelesaikan 20 butir</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>Pre-test dibatasi waktu 14 menit sehingga sedikit yang tuntas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Orang mengikuti KEDUA tes</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Hasil pencocokan nama antar kedua daftar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Orang mengikuti kedua tes sampai TUNTAS</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>Dasar seluruh uji statistik pada laporan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>B. DAFTAR SESI GANDA — BUKTI RINCI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Nama pada ekspor</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Benar</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Salah</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Kosong</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Waktu (detik)</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Sesi dipakai?</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Penilaian</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Sri Suyani</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>tidak</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>Sesi kosong — masuk lalu keluar tanpa menjawab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Sri Suyani*</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>tidak</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>Sesi terputus; sebagian besar butir tidak terjawab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Sri Suyani**</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>255</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Sesi terlengkap; dipakai sebagai data orang ini.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Aqifah</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
+        <is>
+          <t>tidak</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>Sesi kosong — masuk lalu keluar tanpa menjawab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Aqifah*</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>501</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>Sesi terlengkap; dipakai sebagai data orang ini.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>farida johannes</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>328</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>Sesi terlengkap; dipakai sebagai data orang ini.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>farida johannes*</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>tidak</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>Sesi terputus; sebagian besar butir tidak terjawab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Yovita  (post-test)</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>Sesi tuntas 20 butir; dipakai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Yovita*  (post-test)</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>tidak</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>Sesi kosong — tidak satu butir pun dijawab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Enam dari tujuh sesi ganda praktis kosong: peserta masuk lalu keluar tanpa menjawab, atau berhenti setelah beberapa butir. Pola ini sejalan dengan kendala teknis yang sudah dicatat pada laporan pre-test, bukan dengan pengerjaan ulang untuk memperbaiki nilai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>C. DAMPAK TERHADAP ANGKA YANG DILAPORKAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Ukuran pre-test</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Basis 37 sesi</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Basis 33 orang</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Selisih</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Akibatnya</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Rata-rata jawaban benar</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>Angka 33 orang lebih tinggi karena sesi kosong tidak lagi menurunkan rata-rata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>Akurasi kelas (%)</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>Basis orang menaikkan akurasi pre-test sekitar 3 poin persen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>Rata-rata tingkat kesukaran p</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>Selisih terbesar pada satu butir 0,072 (Q20). Peringkat kesukaran butir tidak berubah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>D. YANG TIDAK TERDAMPAK — DAN MENGAPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>•  Tidak satu pun dari tiga orang bersesi ganda pada pre-test (Sri Suyani, Aqifah, farida johannes) termasuk dalam 8 peserta berpasangan. Untuk Yovita pada post-test, sesi tuntas 13 benar yang dipakai, bukan sesi kosongnya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>•  Karena itu seluruh hasil utama laporan TIDAK berubah: rata-rata gain +5,00 butir, uji-t t(7)=3,67, Cohen dz=1,30, uji tanda p=0,0039, dan gain ternormalisasi Hake 0,440.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>•  Yang perlu dikoreksi hanyalah angka deskriptif tingkat kelas pada pre-test bila basisnya dinyatakan sebagai ORANG dan bukan SESI. Kedua basis kini dilaporkan berdampingan pada bagian C di atas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>Data grafik</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>Pre-test</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>Post-test</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Sesi terekam</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Sesi peserta</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Orang unik</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Ikut kedua tes</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Kedua tes tuntas</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B28:H28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B2:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2953,7 +3922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5360,7 +6329,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6015,7 +6984,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
